--- a/astro-site/public/dl/hotel-checklist-templates/BONUS-02-hotel-fb-calendar.xlsx
+++ b/astro-site/public/dl/hotel-checklist-templates/BONUS-02-hotel-fb-calendar.xlsx
@@ -890,7 +890,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Closed adult and kids menus, room and photo booth; no alcohol for minors (21+); book 3–6 months ahead</t>
+          <t>Set adult and kids' menus, private room and photo booth; no alcohol for minors (21+); book 3–6 months ahead</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Thanksgiving buffet or prix fixe menu (turkey), seatings closed early and long-weekend packages</t>
+          <t>Thanksgiving buffet or prix fixe menu (turkey), reservations by seating, booked well ahead, and long-weekend packages</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
